--- a/outputs/pilot_v0.1/manual_scoring_selected_001_009_012_017_020_025.xlsx
+++ b/outputs/pilot_v0.1/manual_scoring_selected_001_009_012_017_020_025.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6501527-53A4-9447-AE97-614B344895B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="17620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="人工评分" sheetId="1" r:id="rId1"/>
